--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484593_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484593_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0431</v>
+        <v>0.2989</v>
       </c>
       <c r="E3" t="n">
-        <v>0.498</v>
+        <v>0.7042</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4549</v>
+        <v>-0.4054</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3215</v>
@@ -688,13 +688,13 @@
         <v>0.733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4986</v>
+        <v>-0.2428</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3492</v>
+        <v>-0.1429</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1495</v>
+        <v>-0.0999</v>
       </c>
       <c r="V3" t="n">
         <v>1.9628</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5933</v>
+        <v>-0.1843</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3026</v>
+        <v>-0.8872</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8959</v>
+        <v>0.7029</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0072</v>
+        <v>0.3751</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3809</v>
+        <v>-0.3108</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3881</v>
+        <v>0.6859</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1654</v>
+        <v>0.7935</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0404</v>
+        <v>0.0433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.125</v>
+        <v>0.7501</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1726</v>
+        <v>-0.4184</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6594</v>
+        <v>-0.3541</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5131</v>
+        <v>-0.0643</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1133</v>
+        <v>0.3392</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0015</v>
+        <v>0.0132</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1148</v>
+        <v>0.326</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8827</v>
+        <v>0.3843</v>
       </c>
       <c r="W4" t="n">
         <v>0.3219</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2047</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6572</v>
+        <v>-0.5989</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2858</v>
+        <v>1.2209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6286</v>
+        <v>-1.8199</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3751</v>
+        <v>-3.8092</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3108</v>
+        <v>-0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6859</v>
+        <v>-2.8883</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7935</v>
+        <v>-0.6217</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0433</v>
+        <v>1.1763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7501</v>
+        <v>-1.7981</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4184</v>
+        <v>-3.1875</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3541</v>
+        <v>-2.0973</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0643</v>
+        <v>-1.0902</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R5" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1337</v>
+        <v>-0.0922</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3854</v>
+        <v>-0.2356</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2517</v>
+        <v>0.1435</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3843</v>
+        <v>3.3025</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>3.1778</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0623</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8938</v>
+        <v>-0.7801</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003</v>
+        <v>1.1653</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8941</v>
+        <v>-1.9455</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6967</v>
+        <v>-0.0072</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2799</v>
+        <v>0.3809</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4167</v>
+        <v>-0.3881</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5668</v>
+        <v>1.1654</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0742</v>
+        <v>1.0404</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.641</v>
+        <v>0.125</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1299</v>
+        <v>-1.1726</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3541</v>
+        <v>-0.6594</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2243</v>
+        <v>-0.5131</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.1833</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>0.641</v>
+        <v>-0.0735</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7504</v>
+        <v>-0.1387</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1094</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2047</v>
+        <v>-0.8827</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
         <v>-1.2047</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2522</v>
+        <v>-1.2784</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5115</v>
+        <v>-0.3843</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.7636</v>
+        <v>-0.8941</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3664</v>
+        <v>-0.6967</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4591</v>
+        <v>-0.2799</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9073</v>
+        <v>-0.4167</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0384</v>
+        <v>-0.5668</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1891</v>
+        <v>0.0742</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1508</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3281</v>
+        <v>-0.1299</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.27</v>
+        <v>-0.3541</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0581</v>
+        <v>0.2243</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R7" t="n">
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9023</v>
+        <v>0.2564</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0317</v>
+        <v>0.3658</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8706</v>
+        <v>-0.1094</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>-1.2047</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8559</v>
+        <v>-1.2047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2641</v>
+        <v>-2.163</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6301</v>
+        <v>-2.7667</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8942</v>
+        <v>0.6037</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8092</v>
+        <v>-4.0516</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.921</v>
+        <v>-2.2214</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8883</v>
+        <v>-1.8302</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6217</v>
+        <v>-2.6042</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1763</v>
+        <v>-0.7743</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7981</v>
+        <v>-1.8299</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1875</v>
+        <v>-1.4474</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0973</v>
+        <v>-1.4471</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0902</v>
+        <v>-0.0003</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7574</v>
+        <v>0.4989</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8265</v>
+        <v>0.0208</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.4781</v>
       </c>
       <c r="V8" t="n">
-        <v>3.3025</v>
+        <v>-0.2596</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1778</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1246</v>
+        <v>-0.2596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2702</v>
+        <v>-2.9723</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.973</v>
+        <v>1.1381</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7028</v>
+        <v>-4.1104</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0516</v>
+        <v>-2.3664</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2214</v>
+        <v>-1.4591</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8302</v>
+        <v>-0.9073</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6042</v>
+        <v>-0.0384</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7743</v>
+        <v>-0.1891</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8299</v>
+        <v>0.1508</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4474</v>
+        <v>-2.3281</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4471</v>
+        <v>-1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0003</v>
+        <v>-1.0581</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6493</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3917</v>
+        <v>1.1821</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1855</v>
+        <v>0.6584</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5772</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2596</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2596</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5527</v>
+        <v>-3.2965</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3546</v>
+        <v>-3.3957</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1981</v>
+        <v>0.0992</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8513</v>
@@ -1234,13 +1234,13 @@
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.1595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0384</v>
+        <v>-0.0795</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0582</v>
+        <v>0.2391</v>
       </c>
       <c r="V10" t="n">
         <v>0.3115</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2102</v>
+        <v>-3.9162</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7793</v>
+        <v>-2.4358</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4309</v>
+        <v>-1.4804</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0573</v>
@@ -1312,13 +1312,13 @@
         <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1974</v>
+        <v>0.0965</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5875</v>
+        <v>-0.244</v>
       </c>
       <c r="U11" t="n">
-        <v>0.39</v>
+        <v>0.3405</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5889</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8004</v>
+        <v>-4.7125</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4589</v>
+        <v>-4.1976</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3415</v>
+        <v>-0.5149</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1062</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3351</v>
+        <v>-0.2472</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5094</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4357</v>
+        <v>0.2622</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8931</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1441</v>
+        <v>-6.7347</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4805</v>
+        <v>-3.0959</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6636</v>
+        <v>-3.6388</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8691</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6434</v>
+        <v>-0.234</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6433</v>
+        <v>-0.2586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0001</v>
+        <v>0.0247</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1497</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.6454</v>
+        <v>-6.8013</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.8843</v>
+        <v>-6.2384</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7611</v>
+        <v>-0.5629</v>
       </c>
       <c r="G14" t="n">
         <v>-4.0643</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1145</v>
+        <v>-0.2704</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2111</v>
+        <v>-0.5652</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.2949</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1838</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-32.9903</v>
+        <v>-31.8891</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.0237</v>
+        <v>-17.9229</v>
       </c>
       <c r="F15" t="n">
         <v>-13.9665</v>
@@ -1594,7 +1594,7 @@
         <v>-15.9654</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.610100000000001</v>
+        <v>-5.6101</v>
       </c>
       <c r="J15" t="n">
         <v>-3.9804</v>
@@ -1624,10 +1624,10 @@
         <v>10.9954</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2714999999999999</v>
+        <v>1.3725</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.217000000000001</v>
+        <v>-1.1157</v>
       </c>
       <c r="U15" t="n">
         <v>2.4886</v>
@@ -1639,13 +1639,13 @@
         <v>7.331799999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.855499999999999</v>
+        <v>-9.855500000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.4172</v>
+        <v>6.6075</v>
       </c>
       <c r="E16" t="n">
-        <v>4.522</v>
+        <v>3.5536</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8952</v>
+        <v>3.0539</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9206</v>
+        <v>3.1369</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9015</v>
+        <v>0.0305</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0191</v>
+        <v>3.1065</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0521</v>
+        <v>2.971</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6098</v>
+        <v>-1.0653</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5577</v>
+        <v>4.0363</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1315</v>
+        <v>0.1659</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7083</v>
+        <v>1.0958</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5768</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2828</v>
+        <v>2.5656</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4129</v>
+        <v>-0.0505</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0355</v>
+        <v>-0.3729</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3774</v>
+        <v>0.3224</v>
       </c>
       <c r="V16" t="n">
-        <v>3.8009</v>
+        <v>0.9554</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8009</v>
+        <v>0.9554</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.1295</v>
+        <v>6.4536</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6497</v>
+        <v>4.4258</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4798</v>
+        <v>2.0278</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1369</v>
+        <v>0.9206</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0305</v>
+        <v>0.9015</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1065</v>
+        <v>0.0191</v>
       </c>
       <c r="J17" t="n">
-        <v>2.971</v>
+        <v>1.0521</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0653</v>
+        <v>1.6098</v>
       </c>
       <c r="L17" t="n">
-        <v>4.0363</v>
+        <v>-0.5577</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1659</v>
+        <v>-0.1315</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0958</v>
+        <v>-0.7083</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0.5768</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5656</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5285</v>
+        <v>0.4493</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2767</v>
+        <v>-0.0607</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2517</v>
+        <v>0.51</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9554</v>
+        <v>3.8009</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9554</v>
+        <v>3.8009</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0979</v>
+        <v>3.5153</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1681</v>
+        <v>0.2935</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0702</v>
+        <v>3.2218</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5139</v>
+        <v>2.3672</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0685</v>
+        <v>2.6494</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4454</v>
+        <v>-0.2822</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5617</v>
+        <v>1.4731</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4367</v>
+        <v>2.5884</v>
       </c>
       <c r="L18" t="n">
-        <v>0.125</v>
+        <v>-1.1154</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9522</v>
+        <v>0.8941</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6318</v>
+        <v>0.0609</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3204</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1991</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4318</v>
+        <v>0.0094</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6606</v>
+        <v>-0.2579</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2288</v>
+        <v>0.2673</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.267</v>
+        <v>0.9554</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>1.2774</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5339</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8758</v>
+        <v>3.5117</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8758</v>
+        <v>3.5527</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.041</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8758</v>
+        <v>3.5139</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6256</v>
+        <v>3.0685</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2502</v>
+        <v>0.4454</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8758</v>
+        <v>2.5617</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6256</v>
+        <v>2.4367</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2502</v>
+        <v>0.125</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.9522</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.6318</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.3204</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.0181</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.276</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2579</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7954</v>
+        <v>2.9483</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4909</v>
+        <v>-0.4181</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2863</v>
+        <v>3.3664</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1112</v>
+        <v>0.8727</v>
       </c>
       <c r="H20" t="n">
-        <v>2.185</v>
+        <v>-0.1628</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0738</v>
+        <v>1.0355</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4171</v>
+        <v>-0.046</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9073</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4902</v>
+        <v>-0.6312</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.9187</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2777</v>
+        <v>-0.748</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4164</v>
+        <v>1.6667</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0158</v>
+        <v>-0.3665</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1991</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8124</v>
+        <v>0.3529</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4193</v>
+        <v>-0.0056</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3931</v>
+        <v>0.3586</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3115</v>
+        <v>0.6231</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.7094</v>
+        <v>2.8758</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.322</v>
+        <v>2.8758</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0313</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8727</v>
+        <v>2.8758</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1628</v>
+        <v>1.6256</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0355</v>
+        <v>1.2502</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.046</v>
+        <v>2.8758</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5852000000000001</v>
+        <v>1.6256</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6312</v>
+        <v>1.2502</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9187</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.748</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6667</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0905</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0235</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2711</v>
+        <v>2.3726</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0911</v>
+        <v>2.5571</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3622</v>
+        <v>-0.1845</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3672</v>
+        <v>1.761</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6494</v>
+        <v>1.2641</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2822</v>
+        <v>0.4969</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4731</v>
+        <v>1.923</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5884</v>
+        <v>1.1054</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1154</v>
+        <v>0.8176</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8941</v>
+        <v>-0.162</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0609</v>
+        <v>0.1587</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.3207</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1991</v>
+        <v>-0.1833</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3823</v>
+        <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2348</v>
+        <v>0.1011</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6425</v>
+        <v>-0.138</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5923</v>
+        <v>0.2391</v>
       </c>
       <c r="V22" t="n">
+        <v>-0.9554</v>
+      </c>
+      <c r="W22" t="n">
         <v>0.9554</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.2774</v>
-      </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.953</v>
+        <v>2.1849</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3648</v>
+        <v>-1.164</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4118</v>
+        <v>3.3489</v>
       </c>
       <c r="G23" t="n">
-        <v>1.761</v>
+        <v>2.1112</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2641</v>
+        <v>2.185</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4969</v>
+        <v>-0.0738</v>
       </c>
       <c r="J23" t="n">
-        <v>1.923</v>
+        <v>1.4171</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1054</v>
+        <v>1.9073</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8176</v>
+        <v>-0.4902</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.162</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1587</v>
+        <v>0.2777</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3207</v>
+        <v>0.4164</v>
       </c>
       <c r="P23" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3186</v>
+        <v>0.2019</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3303</v>
+        <v>-0.2537</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0118</v>
+        <v>0.4557</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9554</v>
+        <v>-0.3115</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9554</v>
+        <v>-0.3115</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2305</v>
+        <v>1.6341</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3482</v>
+        <v>-1.4443</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5786</v>
+        <v>3.0784</v>
       </c>
       <c r="G24" t="n">
         <v>1.9548</v>
@@ -2326,13 +2326,13 @@
         <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3578</v>
+        <v>0.0458</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3318</v>
+        <v>-0.428</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.026</v>
+        <v>0.4738</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. LE BERRE CASTILLO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2001</v>
+        <v>1.5496</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1132</v>
+        <v>0.4564</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3134</v>
+        <v>1.0932</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.0225</v>
+        <v>2.1416</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0415</v>
+        <v>1.3692</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.981</v>
+        <v>0.7724</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.868</v>
+        <v>1.9282</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1116</v>
+        <v>1.8607</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.7564</v>
+        <v>0.0674</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1544</v>
+        <v>0.2134</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0701</v>
+        <v>-0.4916</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2246</v>
+        <v>0.705</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6728</v>
+        <v>-0.27</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0565</v>
+        <v>-0.3722</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7294</v>
+        <v>0.1022</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6335</v>
+        <v>-0.3219</v>
       </c>
       <c r="W25" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2774</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. LE BERRE CASTILLO</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.0543</v>
+        <v>0.9122</v>
       </c>
       <c r="E26" t="n">
-        <v>0.168</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8863</v>
+        <v>0.8459</v>
       </c>
       <c r="G26" t="n">
-        <v>2.1416</v>
+        <v>1.617</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3692</v>
+        <v>1.7067</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7724</v>
+        <v>-0.0897</v>
       </c>
       <c r="J26" t="n">
-        <v>1.9282</v>
+        <v>1.2495</v>
       </c>
       <c r="K26" t="n">
-        <v>1.8607</v>
+        <v>1.1146</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0674</v>
+        <v>0.1349</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2134</v>
+        <v>0.3676</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4916</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.705</v>
+        <v>-0.2246</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7653</v>
+        <v>0.3343</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6606</v>
+        <v>-0.267</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1047</v>
+        <v>0.6012</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9311</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2585</v>
+        <v>-1.1132</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6725</v>
+        <v>1.777</v>
       </c>
       <c r="G27" t="n">
-        <v>1.617</v>
+        <v>-2.0225</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7067</v>
+        <v>-0.0415</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0897</v>
+        <v>-1.981</v>
       </c>
       <c r="J27" t="n">
-        <v>1.2495</v>
+        <v>-1.868</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1146</v>
+        <v>-0.1116</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1349</v>
+        <v>-1.7564</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3676</v>
+        <v>-0.1544</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="O27" t="n">
         <v>-0.2246</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3532</v>
+        <v>1.1365</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.0746</v>
+        <v>-0.0565</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4278</v>
+        <v>1.193</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.5889</v>
+        <v>0.6335</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.5889</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="28">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>32.9904</v>
+        <v>35.55449999999999</v>
       </c>
       <c r="E29" t="n">
         <v>13.9666</v>
       </c>
       <c r="F29" t="n">
-        <v>19.0236</v>
+        <v>21.5878</v>
       </c>
       <c r="G29" t="n">
         <v>21.5753</v>
@@ -2716,13 +2716,13 @@
         <v>20.1582</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.2714999999999999</v>
+        <v>2.2926</v>
       </c>
       <c r="T29" t="n">
-        <v>-2.4883</v>
+        <v>-2.4885</v>
       </c>
       <c r="U29" t="n">
-        <v>2.2171</v>
+        <v>4.7812</v>
       </c>
       <c r="V29" t="n">
         <v>2.523599999999999</v>
